--- a/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
+++ b/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jsher24/Desktop/Traders@SMU/polymarket-copy-trading-bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130D8A54-9B0D-46AE-980D-0D691E454EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1FE7F87-70C7-BE42-B038-642D38B19EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="19200" windowHeight="11170" xr2:uid="{4F75D300-4D31-744C-B381-2925FE9CB6B9}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16280" xr2:uid="{87DC968E-4842-CC4D-984F-A7EACFB7F109}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="tracked_pairs_links" localSheetId="0">Sheet1!$A$1:$I$26</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,65 +38,442 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{C23EC20A-25F1-C54A-A561-59EE122F401C}" name="tracked_pairs_links" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/jsher24/Desktop/Traders@SMU/polymarket-copy-trading-bot/tracked_pairs_links.csv" tab="0" comma="1">
+      <textFields count="9">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="136">
   <si>
     <t>pair_id</t>
   </si>
   <si>
+    <t>title_clean</t>
+  </si>
+  <si>
+    <t>category_tag</t>
+  </si>
+  <si>
+    <t>similarity_score</t>
+  </si>
+  <si>
     <t>poly_market_id</t>
   </si>
   <si>
+    <t>poly_slug</t>
+  </si>
+  <si>
+    <t>poly_url</t>
+  </si>
+  <si>
     <t>kalshi_market_id</t>
   </si>
   <si>
-    <t>title_clean</t>
-  </si>
-  <si>
-    <t>similarity_score</t>
-  </si>
-  <si>
-    <t>category_tag</t>
-  </si>
-  <si>
-    <t>poly_url</t>
-  </si>
-  <si>
     <t>kalshi_url</t>
   </si>
   <si>
-    <t>poly_slug</t>
+    <t>pair-0001</t>
+  </si>
+  <si>
+    <t>will anthony edwards win the 2025 2026 nba mvp</t>
+  </si>
+  <si>
+    <t>sports</t>
   </si>
   <si>
     <t>will-anthony-edwards-win-the-20252026-nba-mvp</t>
   </si>
   <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>Will Anthony Edwards win the 2025–2026 NBA MVP?</t>
-  </si>
-  <si>
-    <t>0x33882fdaa147a31a1231293615b6e249ee8cf790fce9d8dc14f312f7b3cc0e30</t>
-  </si>
-  <si>
-    <t>https://polymarket.com/market/will-anthony-edwards-win-the-20252026-nba-mvp</t>
+    <t>https://polymarket.com/event/will-anthony-edwards-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026B8778AB5DFA-8E764236B07</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026B8778AB5DFA-8E764236B07</t>
+  </si>
+  <si>
+    <t>pair-0002</t>
+  </si>
+  <si>
+    <t>will shai gilgeous alexander win the 2025 2026 nba mvp</t>
+  </si>
+  <si>
+    <t>will-shai-gilgeous-alexander-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-shai-gilgeous-alexander-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>KXMVESPORTSMULTIGAMEEXTENDED-S202686D24CEB3AE-CB0CD9C639F</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVESPORTSMULTIGAMEEXTENDED-S202686D24CEB3AE-CB0CD9C639F</t>
+  </si>
+  <si>
+    <t>pair-0003</t>
+  </si>
+  <si>
+    <t>will the new orleans pelicans win the 2026 nba finals</t>
+  </si>
+  <si>
+    <t>will-the-new-orleans-pelicans-win-the-2026-nba-finals</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-the-new-orleans-pelicans-win-the-2026-nba-finals</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20269EF9FBC3480-47D2A59B1EE</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20269EF9FBC3480-47D2A59B1EE</t>
+  </si>
+  <si>
+    <t>pair-0004</t>
+  </si>
+  <si>
+    <t>will cade cunningham win the 2025 2026 nba mvp</t>
+  </si>
+  <si>
+    <t>will-cade-cunningham-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-cade-cunningham-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026084A0917FFB-AA1EB963F58</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026084A0917FFB-AA1EB963F58</t>
+  </si>
+  <si>
+    <t>pair-0005</t>
+  </si>
+  <si>
+    <t>will jaylen brown win the 2025 2026 nba mvp</t>
+  </si>
+  <si>
+    <t>will-jaylen-brown-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-jaylen-brown-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026886F9862E1F-C6FFDD876E0</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026886F9862E1F-C6FFDD876E0</t>
+  </si>
+  <si>
+    <t>pair-0006</t>
+  </si>
+  <si>
+    <t>will the los angeles kings win the 2026 nhl stanley cup</t>
+  </si>
+  <si>
+    <t>will-the-los-angeles-kings-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-the-los-angeles-kings-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20263A9D95419E6-C33AA0320A8</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20263A9D95419E6-C33AA0320A8</t>
+  </si>
+  <si>
+    <t>pair-0007</t>
+  </si>
+  <si>
+    <t>will lebron james win the 2028 democratic presidential nomination</t>
+  </si>
+  <si>
+    <t>politics</t>
+  </si>
+  <si>
+    <t>will-lebron-james-win-the-2028-democratic-presidential-nomination</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-lebron-james-win-the-2028-democratic-presidential-nomination</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20264F2FAE36450-8279BDF825B</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20264F2FAE36450-8279BDF825B</t>
+  </si>
+  <si>
+    <t>pair-0008</t>
+  </si>
+  <si>
+    <t>will real madrid win the 2025 26 champions league</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>will-real-madrid-win-the-202526-champions-league</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-real-madrid-win-the-202526-champions-league</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026CD65ABB47E5-A857D99647F</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026CD65ABB47E5-A857D99647F</t>
   </si>
   <si>
     <t>pair-0009</t>
   </si>
   <si>
-    <t>KXNBAMVP-26-AEDW</t>
-  </si>
-  <si>
-    <t>https://kalshi.com/markets/KXNBAMVP-26-AEDW</t>
+    <t>will the oklahoma city thunder win the 2026 nba finals</t>
+  </si>
+  <si>
+    <t>will-the-oklahoma-city-thunder-win-the-2026-nba-finals</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-the-oklahoma-city-thunder-win-the-2026-nba-finals</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S202679CF7D60E0F-C290E82693C</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S202679CF7D60E0F-C290E82693C</t>
+  </si>
+  <si>
+    <t>pair-0010</t>
+  </si>
+  <si>
+    <t>will tyrese maxey win the 2025 2026 nba mvp</t>
+  </si>
+  <si>
+    <t>will-tyrese-maxey-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-tyrese-maxey-win-the-20252026-nba-mvp</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026D37CBF334D1-B7797C46DB2</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026D37CBF334D1-B7797C46DB2</t>
+  </si>
+  <si>
+    <t>pair-0011</t>
+  </si>
+  <si>
+    <t>will bayern munich win the 2025 26 champions league</t>
+  </si>
+  <si>
+    <t>will-bayern-munich-win-the-202526-champions-league</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-bayern-munich-win-the-202526-champions-league</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026D04FC0A1D8D-F19E1E0A84A</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026D04FC0A1D8D-F19E1E0A84A</t>
+  </si>
+  <si>
+    <t>pair-0012</t>
+  </si>
+  <si>
+    <t>will the new york rangers win the 2026 nhl stanley cup</t>
+  </si>
+  <si>
+    <t>will-the-new-york-rangers-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-the-new-york-rangers-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026286BEFF7D0B-CF636424568</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026286BEFF7D0B-CF636424568</t>
+  </si>
+  <si>
+    <t>pair-0013</t>
+  </si>
+  <si>
+    <t>will dortmund win the 2025 26 bundesliga</t>
+  </si>
+  <si>
+    <t>will-dortmund-win-the-202526-bundesliga</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-dortmund-win-the-202526-bundesliga</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S202692EFD37F4E2-7935C052F97</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S202692EFD37F4E2-7935C052F97</t>
+  </si>
+  <si>
+    <t>pair-0014</t>
+  </si>
+  <si>
+    <t>new rihanna album before gta vi</t>
+  </si>
+  <si>
+    <t>new-rhianna-album-before-gta-vi-926</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/new-rhianna-album-before-gta-vi-926</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20264C795D7A4D0-13DB55E5D1C</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20264C795D7A4D0-13DB55E5D1C</t>
+  </si>
+  <si>
+    <t>pair-0015</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20266FEA88A399C-95EF8FC89FA</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20266FEA88A399C-95EF8FC89FA</t>
+  </si>
+  <si>
+    <t>pair-0016</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20269129EBB8407-0DD75E131F0</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20269129EBB8407-0DD75E131F0</t>
+  </si>
+  <si>
+    <t>pair-0017</t>
+  </si>
+  <si>
+    <t>will the carolina hurricanes win the 2026 nhl stanley cup</t>
+  </si>
+  <si>
+    <t>will-the-carolina-hurricanes-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-the-carolina-hurricanes-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20262C88EEABD53-B63A1EF7391</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20262C88EEABD53-B63A1EF7391</t>
+  </si>
+  <si>
+    <t>pair-0018</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S202644C863E6EF2-0A7CDCE94C1</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S202644C863E6EF2-0A7CDCE94C1</t>
+  </si>
+  <si>
+    <t>pair-0019</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026C7A2D2069BB-9A6B57659B1</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026C7A2D2069BB-9A6B57659B1</t>
+  </si>
+  <si>
+    <t>pair-0020</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20267CD770A6736-1B2210915AB</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20267CD770A6736-1B2210915AB</t>
+  </si>
+  <si>
+    <t>pair-0021</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S20265773B80332E-2A7CB463315</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S20265773B80332E-2A7CB463315</t>
+  </si>
+  <si>
+    <t>pair-0022</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026E699A91E46C-FA16BD2B650</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026E699A91E46C-FA16BD2B650</t>
+  </si>
+  <si>
+    <t>pair-0023</t>
+  </si>
+  <si>
+    <t>will the florida panthers win the 2026 nhl stanley cup</t>
+  </si>
+  <si>
+    <t>will-the-florida-panthers-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>https://polymarket.com/event/will-the-florida-panthers-win-the-2026-nhl-stanley-cup</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S202678CC5B2637C-BECFF231FBC</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S202678CC5B2637C-BECFF231FBC</t>
+  </si>
+  <si>
+    <t>pair-0024</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026775CB00200D-10DF48D3E3F</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026775CB00200D-10DF48D3E3F</t>
+  </si>
+  <si>
+    <t>pair-0025</t>
+  </si>
+  <si>
+    <t>KXMVECROSSCATEGORY-S2026EAC63F803B6-582E9DB1C12</t>
+  </si>
+  <si>
+    <t>https://kalshi.com/markets/KXMVECROSSCATEGORY-S2026EAC63F803B6-582E9DB1C12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time to expiration (2 months out) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -101,21 +481,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -127,16 +505,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -152,10 +528,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="tracked_pairs_links" connectionId="1" xr16:uid="{51C24B16-09C0-204E-B6A8-A5ABF8C181F7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,7 +573,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -299,7 +679,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,84 +821,784 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FECAC60-48D7-43F9-806E-3C5F68959A94}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3B2B3B-E1EC-0F45-9EEF-1EAC6924D9DF}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.4140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.4140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+        <v>0.18179999999999999</v>
+      </c>
+      <c r="E2">
+        <v>564165</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
       <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="E3">
+        <v>564162</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="E4">
+        <v>553875</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="E5">
+        <v>564168</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="E6">
+        <v>564175</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="E7">
+        <v>553831</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="E8">
+        <v>559681</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="E9">
+        <v>566139</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>0.1429</v>
+      </c>
+      <c r="E10">
+        <v>553856</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>0.1333</v>
+      </c>
+      <c r="E11">
+        <v>564183</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12">
+        <v>0.1333</v>
+      </c>
+      <c r="E12">
+        <v>566142</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>0.125</v>
+      </c>
+      <c r="E13">
+        <v>553836</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14">
+        <v>0.125</v>
+      </c>
+      <c r="E14">
+        <v>566538</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="E15">
+        <v>540817</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="E16">
+        <v>540817</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="E17">
+        <v>540817</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="E18">
+        <v>553824</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E19">
+        <v>540817</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="E20">
+        <v>553824</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="E21">
+        <v>553824</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="E22">
+        <v>540817</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="E23">
+        <v>540817</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="E24">
+        <v>553825</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="E25">
+        <v>540817</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" t="s">
+        <v>130</v>
+      </c>
+      <c r="I25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="E26">
+        <v>553824</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
+++ b/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1159"/>
+  <dimension ref="A1:K1161"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -51744,6 +51744,100 @@
         </is>
       </c>
     </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>pair-0170</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Howard Bison vs. UMBC Retrievers</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>0x63f4859ba6b341ec56c53fc5d49e371def1dab41ccae6e02fb05166d8b96f5fd</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>cbb-howrd-umbc-2026-03-17</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-howrd-umbc-2026-03-17</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR17UMBCHOW-HOW</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR17UMBCHOW-HOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>pair-0171</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Howard Bison vs. UMBC Retrievers</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>0x63f4859ba6b341ec56c53fc5d49e371def1dab41ccae6e02fb05166d8b96f5fd</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>cbb-howrd-umbc-2026-03-17</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-howrd-umbc-2026-03-17</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR17UMBCHOW-UMBC</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR17UMBCHOW-UMBC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId1"/>

--- a/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
+++ b/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1161"/>
+  <dimension ref="A1:K1162"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -51838,6 +51838,53 @@
         </is>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>pair-0172</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>North Carolina State Wolfpack vs. Texas Longhorns</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>0x68cbb3bd267f30f766bc22ae7dd3ea0263c3abe3dc769eb63f98a12cd3b7ebfb</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>cbb-ncst-tx-2026-03-17</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ncst-tx-2026-03-17</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR17TEXNCST-TEX</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR17TEXNCST-TEX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId1"/>

--- a/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
+++ b/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1162"/>
+  <dimension ref="A1:K1207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -51885,6 +51885,2121 @@
         </is>
       </c>
     </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>pair-0175</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Will Duke advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>0xe2d9d869dd27bb86421791d08663c8b76de66d324adf51041cf77362ce046d78</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>will-duke-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-duke-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-DUKE</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-DUKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>pair-0176</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Will Iowa State advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>0x2521994f8558f5355377e2788822f7f2a0284840ee8ed4faf613da5496f2ee84</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>will-iowa-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-iowa-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-IOWA</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-IOWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>pair-0178</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Will Arkansas advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>0x49edf6d686d1140f52e56ae0fa17a071b6e7afc98806cbcb08a5538dc66d5235</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>will-arkansas-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-arkansas-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-ARK</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-ARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>pair-0179</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Will Michigan State advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>0xaa50bcf61975bd2fff333b3b6b1f48d60828a2f4235e205b3d11d7e9b8d47d19</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>will-michigan-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-michigan-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-MSU</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-MSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>pair-0181</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Will Houston advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>0x8a4fbb770febf0e499d25b0c1ebd912af18a9aa9e329ecbcb14d54c53748891c</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>will-houston-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-houston-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-HOU</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-HOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>pair-0182</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Will Iowa State advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>0x2521994f8558f5355377e2788822f7f2a0284840ee8ed4faf613da5496f2ee84</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>will-iowa-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-iowa-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-ISU</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-ISU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>pair-0185</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Will Michigan State advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>0xaa50bcf61975bd2fff333b3b6b1f48d60828a2f4235e205b3d11d7e9b8d47d19</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>will-michigan-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-michigan-state-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-MICH</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-MICH</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>pair-0186</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Will Nebraska advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>0x792212136b51b112046ac842549027a5a4c6b8c5007a06d81854f1f204201e5f</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>will-nebraska-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-nebraska-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-NEB</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-NEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>pair-0188</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Will Purdue advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>0xa434c410a5eada0684f4d038dc110dfd392388eb907f355b91297da3f9156a36</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>will-purdue-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-purdue-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-PUR</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-PUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>pair-0189</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Will St. John’s advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>0x5c81dad9ab9b082ddadb48cd71d04be87919208f1bd31d435039cac204effed9</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>will-st-johns-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-st-johns-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-SJU</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-SJU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>pair-0177</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Will Texas advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>0x626fa9d0ae80e1a33d7030a3ea73644dc314cfdee765e363b5b6443042ba1149</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>will-texas-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-texas-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-TEX</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-TEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>pair-0178</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Will Arizona advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>0xb96184a452133bd7699459fcf63e75b2fcb410d79abdf90fb021e96addc61445</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>will-arizona-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-arizona-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-ARIZ</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-ARIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>pair-0181</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Will Iowa advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>0x5f1aae9367cfe314fff3cb0ba0c2003617ece162dde9c90f8c2358d3db9d418b</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>will-iowa-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-iowa-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-IOWA</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-IOWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>pair-0187</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Will Alabama advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>0x19bdd890d4141671057fc2cbccc4875064b20aaa24995aabc045d68ba33e29e4</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>will-alabama-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-alabama-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-ALA</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-ALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>pair-0188</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Will Michigan advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>0xc6f35e36bc9f359471041fb900d9ce1bed8ad2e3d4d5645b20912b9c22cb3048</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>will-michigan-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-michigan-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-MICH</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-MICH</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>pair-0191</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Will Illinois advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>0x54470c3162b0581965d7ca36c2e2e6432cd7a91ea1b39a2698ce921fcc09900b</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>will-illinois-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-illinois-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-ILL</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-ILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>pair-0194</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Will Tennessee advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>0x925ff5e1b6abc53c21c884dbc28fd1efb18d6495ce41799f980ff4d3bc33f26d</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>will-tennessee-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-tennessee-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-TENN</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-TENN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>pair-0195</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Will UConn advance to the Final Four?</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>0xb39306b2f950db1609501f00ce0e0cfbc113b38ce2d8dacfcdbd6c94ca067915</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>will-uconn-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-uconn-advance-to-the-final-four</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26F4-CONN</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26F4-CONN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>pair-0196</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Will Trump visit China by March 31?</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>0xffff6c984d7adab19e799c46d1a478d5ab6483479b41f9639d04617f07a8bab0</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>will-trump-visit-china-by-march-31</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-trump-visit-china-by-march-31</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>KXTRUMPCHINA-26-MAY15</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXTRUMPCHINA-26-MAY15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>pair-0197</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Will Trump visit China by April 30?</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>0x48fbf70c1713e71a405052bc4641e26dbba435fa557672c4040763c901cbf606</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>will-trump-visit-china-by-april-30</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-trump-visit-china-by-april-30</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>KXTRUMPCHINA-26-APR24</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXTRUMPCHINA-26-APR24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>pair-0198</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Will monthly inflation increase by 0.8% or more in March?</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>0xde59eb12d813c8f9bd5988c4ec2227c4218468cef5058cf4793756c31e9e4538</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>will-monthly-inflation-increase-by-0pt8-or-more-in-march-692</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-monthly-inflation-increase-by-0pt8-or-more-in-march-692</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>KXECONSTATCPI-26MAR-T1.2</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXECONSTATCPI-26MAR-T1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>pair-0199</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Texas Longhorns vs. Purdue Boilermakers</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>0xeb2456400fb4d6de5f8bf556449b86880cf4fba96291d4d1bd9158e8f62e9020</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>cbb-tx-pur-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-tx-pur-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26TEXPUR-PUR</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26TEXPUR-PUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>pair-0200</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Texas Longhorns vs. Purdue Boilermakers</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>0xeb2456400fb4d6de5f8bf556449b86880cf4fba96291d4d1bd9158e8f62e9020</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>cbb-tx-pur-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-tx-pur-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26TEXPUR-TEX</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26TEXPUR-TEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>pair-0201</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Nebraska Cornhuskers vs. Iowa Hawkeyes</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>0xe96bab86f43e9ae8647eedb5ed680747a8875571c027d11f1f2bae39867d4209</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>cbb-nebr-iowa-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-nebr-iowa-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26IOWANEB-NEB</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26IOWANEB-NEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>pair-0202</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Nebraska Cornhuskers vs. Iowa Hawkeyes</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>0xe96bab86f43e9ae8647eedb5ed680747a8875571c027d11f1f2bae39867d4209</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>cbb-nebr-iowa-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-nebr-iowa-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26IOWANEB-IOWA</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26IOWANEB-IOWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>pair-0203</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Arkansas Razorbacks vs. Arizona Wildcats</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>0x0846ea47be5f14e6dca27e14581d79c09583ca653719ce37dc054494e3997952</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>cbb-ark-arz-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ark-arz-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26ARKARIZ-ARIZ</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26ARKARIZ-ARIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>pair-0204</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Arkansas Razorbacks vs. Arizona Wildcats</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>0x0846ea47be5f14e6dca27e14581d79c09583ca653719ce37dc054494e3997952</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>cbb-ark-arz-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ark-arz-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26ARKARIZ-ARK</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26ARKARIZ-ARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>pair-0205</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Illinois Fighting Illini vs. Houston Cougars</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>0x742cccb8094536132d2afee783308a6eb3498a094f2082dc26dd13bfd0bf3c2b</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>cbb-ill-hou-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ill-hou-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26ILLHOU-HOU</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26ILLHOU-HOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>pair-0206</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Illinois Fighting Illini vs. Houston Cougars</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>0x742cccb8094536132d2afee783308a6eb3498a094f2082dc26dd13bfd0bf3c2b</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>cbb-ill-hou-2026-03-26</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ill-hou-2026-03-26</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR26ILLHOU-ILL</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR26ILLHOU-ILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>pair-0207</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>St. John's Red Storm vs. Duke Blue Devils</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>0x891e9e5612fb38538cfc8e972e8298f51112d78817f73fbfa73d55f5a2a9b477</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>cbb-stjohn-duke-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-stjohn-duke-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27SJUDUKE-SJU</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27SJUDUKE-SJU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>pair-0208</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>St. John's Red Storm vs. Duke Blue Devils</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>0x891e9e5612fb38538cfc8e972e8298f51112d78817f73fbfa73d55f5a2a9b477</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>cbb-stjohn-duke-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-stjohn-duke-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27SJUDUKE-DUKE</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27SJUDUKE-DUKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>pair-0209</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Alabama Crimson Tide vs. Michigan Wolverines</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>0x682ec1e399ff437b2e0cf7bd7e6df650916186829dfa1112f2f2e81a402ece30</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>cbb-ala-mich-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ala-mich-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27ALAMICH-MICH</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27ALAMICH-MICH</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>pair-0210</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Alabama Crimson Tide vs. Michigan Wolverines</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>0x682ec1e399ff437b2e0cf7bd7e6df650916186829dfa1112f2f2e81a402ece30</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>cbb-ala-mich-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-ala-mich-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27ALAMICH-ALA</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27ALAMICH-ALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>pair-0211</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Michigan State Spartans vs. Connecticut Huskies</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>0xcdedd4460eed2734e4680bf73b08872fe7347931814cda6f2eb570231ba08c03</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>cbb-mst-uconn-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-mst-uconn-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27MSUCONN-MSU</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27MSUCONN-MSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>pair-0212</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Michigan State Spartans vs. Connecticut Huskies</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>0xcdedd4460eed2734e4680bf73b08872fe7347931814cda6f2eb570231ba08c03</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>cbb-mst-uconn-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-mst-uconn-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27MSUCONN-CONN</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27MSUCONN-CONN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>pair-0213</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Tennessee Volunteers vs. Iowa State Cyclones</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>0x8cdf3e7e2322abce8d841b8aae3b1e771a2a2ca1b614a6fd33ef15ee51339609</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>cbb-tenn-iowast-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-tenn-iowast-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27TENNISU-ISU</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27TENNISU-ISU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>pair-0214</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Tennessee Volunteers vs. Iowa State Cyclones</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>0x8cdf3e7e2322abce8d841b8aae3b1e771a2a2ca1b614a6fd33ef15ee51339609</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>cbb-tenn-iowast-2026-03-27</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/cbb-tenn-iowast-2026-03-27</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>KXNCAAMBGAME-26MAR27TENNISU-TENN</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNCAAMBGAME-26MAR27TENNISU-TENN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>pair-0215</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Pelicans vs. Knicks</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>0x1682a7b027b4dfffc14a7e464e79251b522ada4adb665fa84990203405bc22f7</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>nba-nop-nyk-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-nop-nyk-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24NOPNYK-NYK</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24NOPNYK-NYK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>pair-0216</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Pelicans vs. Knicks</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>0x1682a7b027b4dfffc14a7e464e79251b522ada4adb665fa84990203405bc22f7</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>nba-nop-nyk-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-nop-nyk-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24NOPNYK-NOP</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24NOPNYK-NOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>pair-0217</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Kings vs. Hornets</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>0x20cbe1f947287b4be6fe1f06f463e09c24b89de2380779a4ce7ccca73ef6b01e</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>nba-sac-cha-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-sac-cha-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24SACCHA-SAC</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24SACCHA-SAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>pair-0218</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Kings vs. Hornets</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>0x20cbe1f947287b4be6fe1f06f463e09c24b89de2380779a4ce7ccca73ef6b01e</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>nba-sac-cha-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-sac-cha-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24SACCHA-CHA</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24SACCHA-CHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>pair-0219</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Magic vs. Cavaliers</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>0x2f10f76dd83741d6f1b565cab68dd69e30a9299cec124e42633238f10f9812bd</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>nba-orl-cle-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-orl-cle-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24ORLCLE-ORL</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24ORLCLE-ORL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>pair-0220</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Magic vs. Cavaliers</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>0x2f10f76dd83741d6f1b565cab68dd69e30a9299cec124e42633238f10f9812bd</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>nba-orl-cle-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-orl-cle-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24ORLCLE-CLE</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24ORLCLE-CLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>pair-0221</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Nuggets vs. Suns</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>0xbd4c47f29092f81f777211bb56e17a6658e80992fb87db766f679160be3241c3</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>nba-den-phx-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-den-phx-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24DENPHX-PHX</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24DENPHX-PHX</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>pair-0222</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Nuggets vs. Suns</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>0xbd4c47f29092f81f777211bb56e17a6658e80992fb87db766f679160be3241c3</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>nba-den-phx-2026-03-24</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/nba-den-phx-2026-03-24</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>KXNBAGAME-26MAR24DENPHX-DEN</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXNBAGAME-26MAR24DENPHX-DEN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId1"/>

--- a/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
+++ b/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1207"/>
+  <dimension ref="A1:K1208"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -54000,6 +54000,53 @@
         </is>
       </c>
     </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>pair-0223</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Will there be no change in Fed interest rates after the April 2026 meeting?</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>0x36e8ca24d2a13435f519f15580d42b45cdbe3bc425fb39a7c2733260357af0fa</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>will-there-be-no-change-in-fed-interest-rates-after-the-april-2026-meeting</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-there-be-no-change-in-fed-interest-rates-after-the-april-2026-meeting</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>KXFEDDECISION-26APR-H0</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXFEDDECISION-26APR-H0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId1"/>

--- a/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
+++ b/V2/Pairs_for_Kalshi_and_Polymarket.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1208"/>
+  <dimension ref="A1:K1221"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -54047,6 +54047,617 @@
         </is>
       </c>
     </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>pair-0192</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Will Michigan State advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>0x2989038df275f8b6edaea1a12bd97b12197d82895114d5b65133dafa0f7ea999</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>will-michigan-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-michigan-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-MICH</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-MICH</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>pair-0195</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Will Iowa State advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>0xc01a2f52e44859160700ef162274d962d23d059983d83a4b64f29f953cb80136</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>will-iowa-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-iowa-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-ISU</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-ISU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>pair-0196</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Will Arizona advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>0x0e6e5a02c5dcefc6885b6b06f008f133bba7b410a5f298740bf33d7c5d8a8aff</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>will-arizona-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-arizona-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-ARIZ</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-ARIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>pair-0198</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Will Iowa State advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>0xc01a2f52e44859160700ef162274d962d23d059983d83a4b64f29f953cb80136</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>will-iowa-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-iowa-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-IOWA</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-IOWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>pair-0199</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Will Iowa advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>0x21edcdd10df493017114d274eac80a6ccf70f1197309378b36cbf8e5f580745e</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>will-iowa-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-iowa-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-IOWA</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-IOWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>pair-0200</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Will Duke advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>0x78bbf28ce744aa766de7a1f79c832096ccfcc5df93816b407efcc33d40453b99</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>will-duke-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-duke-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-DUKE</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-DUKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>pair-0201</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Will Nebraska advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>0x6324b2a45cba5489c2473087ef09c0565cd469acd3fc79567cccd0eae29170ec</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>will-nebraska-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-nebraska-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-NEB</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-NEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>pair-0202</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Will Tennessee advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>0x03d0764d483ea282db2545ee6176017cc5e775eeb173c8f0f5fb25dbb8bb9e0e</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>will-tennessee-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-tennessee-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-TENN</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-TENN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>pair-0205</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Will Michigan State advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>0x2989038df275f8b6edaea1a12bd97b12197d82895114d5b65133dafa0f7ea999</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>will-michigan-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-michigan-state-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-MSU</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-MSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>pair-0207</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Will Houston advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>0x1d216433fe4c81ef189da239d8dac5d8269dafd7a424291d8a96065254565186</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>will-houston-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-houston-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-HOU</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-HOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>pair-0208</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Will Illinois advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>0x5fcafa2f6112b0104fe7739207108c5aa9b6a8561696036bc77a1af19a066cd5</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>will-illinois-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-illinois-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-ILL</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-ILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>pair-0209</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Will UConn advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>0x529a91317de7353e860a8c453964d5f1b795513676c6fc9f139c26287dbd80f6</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>will-uconn-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-uconn-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-CONN</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-CONN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>pair-0210</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Will Purdue advance to the Quarterfinals?</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>0xdc6b24a3ee1b4fa6da4663ac95196c9f57a0aa64ea6cd36ec2dca018d9d45a07</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>will-purdue-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://polymarket.com/market/will-purdue-advance-to-the-quarterfinals</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>KXMARMADROUND-26E8-PUR</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>https://kalshi.com/markets/KXMARMADROUND-26E8-PUR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId1"/>
